--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
@@ -7254,7 +7254,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
@@ -7254,7 +7254,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250928_100758.xlsx
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
